--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$104</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4441" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4017" uniqueCount="668">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T12:31:04+00:00</t>
+    <t>2025-03-04T08:19:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -659,10 +659,6 @@
     <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
@@ -1594,9 +1590,6 @@
   </si>
   <si>
     <t>Observation.dataAbsentReason.coding.code</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason.coding.display</t>
@@ -1917,43 +1910,10 @@
     <t>Need to be able to identify the target population for proper interpretation.</t>
   </si>
   <si>
-    <t>JDV_J148-ReferenceRangeAppliesTo-CISIS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J148-ReferenceRangeAppliesTo-CISIS/FHIR/JDV-J148-ReferenceRangeAppliesTo-CISIS</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.text</t>
+    <t>Codes identifying the population the reference range applies to.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -2453,11 +2413,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP115"/>
+  <dimension ref="A1:AP104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.09375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="56.09375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.38671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -2481,7 +2441,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="112.42578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -4757,7 +4717,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>122</v>
@@ -4783,10 +4743,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4812,16 +4772,16 @@
         <v>114</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4870,7 +4830,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4905,10 +4865,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4931,17 +4891,17 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4990,7 +4950,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5005,19 +4965,19 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -5025,14 +4985,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5051,17 +5011,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5110,7 +5070,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5125,16 +5085,16 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5145,14 +5105,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5171,16 +5131,16 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5230,7 +5190,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5245,16 +5205,16 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5265,10 +5225,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5294,16 +5254,16 @@
         <v>173</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5328,11 +5288,11 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5350,7 +5310,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>93</v>
@@ -5365,19 +5325,19 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5385,10 +5345,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5411,19 +5371,19 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5451,16 +5411,16 @@
         <v>177</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB25" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5470,7 +5430,7 @@
         <v>120</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5494,10 +5454,10 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5505,13 +5465,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>82</v>
@@ -5533,19 +5493,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5573,11 +5533,11 @@
         <v>177</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5594,7 +5554,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5618,10 +5578,10 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5629,10 +5589,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5747,10 +5707,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5867,10 +5827,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5896,16 +5856,16 @@
         <v>151</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5954,7 +5914,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5975,10 +5935,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5989,10 +5949,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6107,10 +6067,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6227,10 +6187,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6256,65 +6216,65 @@
         <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6335,10 +6295,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6349,10 +6309,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6378,13 +6338,13 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6434,7 +6394,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6455,10 +6415,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6469,10 +6429,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6498,63 +6458,63 @@
         <v>173</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6575,10 +6535,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6589,10 +6549,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6618,14 +6578,14 @@
         <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6674,7 +6634,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6695,10 +6655,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6709,10 +6669,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6735,19 +6695,19 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6796,7 +6756,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6817,10 +6777,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6831,10 +6791,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6860,16 +6820,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6918,7 +6878,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6939,10 +6899,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6953,14 +6913,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6979,19 +6939,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7019,11 +6979,11 @@
         <v>155</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>342</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
       </c>
@@ -7040,7 +7000,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>93</v>
@@ -7055,30 +7015,30 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>348</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7193,10 +7153,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7313,10 +7273,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7342,16 +7302,16 @@
         <v>151</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7388,7 +7348,7 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7398,7 +7358,7 @@
         <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7419,10 +7379,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7433,13 +7393,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
@@ -7464,16 +7424,16 @@
         <v>151</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7522,7 +7482,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7543,10 +7503,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7557,10 +7517,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7675,10 +7635,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7795,10 +7755,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7824,23 +7784,23 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>82</v>
@@ -7882,7 +7842,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7903,10 +7863,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7917,10 +7877,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7946,13 +7906,13 @@
         <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8002,7 +7962,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8023,10 +7983,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8037,10 +7997,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8066,21 +8026,21 @@
         <v>173</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -8122,7 +8082,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8143,10 +8103,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8157,10 +8117,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8186,14 +8146,14 @@
         <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8242,7 +8202,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8263,10 +8223,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8277,10 +8237,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8303,19 +8263,19 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8364,7 +8324,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8385,10 +8345,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8399,10 +8359,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8428,16 +8388,16 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8486,7 +8446,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8507,10 +8467,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8521,10 +8481,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8547,19 +8507,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8608,7 +8568,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8623,19 +8583,19 @@
         <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8643,10 +8603,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8669,16 +8629,16 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8728,7 +8688,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8749,13 +8709,13 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8763,14 +8723,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8789,19 +8749,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8850,7 +8810,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8865,19 +8825,19 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8885,14 +8845,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8911,19 +8871,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8972,7 +8932,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8981,25 +8941,25 @@
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AJ54" t="s" s="2">
+      <c r="AK54" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AK54" t="s" s="2">
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9007,10 +8967,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9036,13 +8996,13 @@
         <v>129</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9092,7 +9052,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9113,13 +9073,13 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9127,10 +9087,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9153,17 +9113,17 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9212,7 +9172,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9227,19 +9187,19 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9247,10 +9207,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9273,19 +9233,19 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9322,26 +9282,26 @@
         <v>82</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE57" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI57" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -9350,30 +9310,30 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>439</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C58" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>82</v>
@@ -9395,19 +9355,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9456,7 +9416,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9465,7 +9425,7 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9474,27 +9434,27 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>439</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9609,10 +9569,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9729,10 +9689,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9755,19 +9715,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9816,7 +9776,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9837,10 +9797,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9851,10 +9811,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9880,65 +9840,65 @@
         <v>173</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q62" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="P62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q62" t="s" s="2">
+      <c r="R62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y62" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="R62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="Y62" t="s" s="2">
+      <c r="Z62" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="Z62" t="s" s="2">
+      <c r="AA62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9959,10 +9919,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9973,10 +9933,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10002,14 +9962,14 @@
         <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10058,7 +10018,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10079,10 +10039,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10093,10 +10053,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10122,72 +10082,72 @@
         <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="S64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF64" t="s" s="2">
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI64" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -10199,10 +10159,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10213,10 +10173,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10242,65 +10202,65 @@
         <v>173</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10321,10 +10281,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10335,10 +10295,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10361,19 +10321,19 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10401,37 +10361,37 @@
         <v>155</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="Z66" t="s" s="2">
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI66" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10446,7 +10406,7 @@
         <v>196</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10457,10 +10417,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10575,10 +10535,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10669,7 +10629,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>122</v>
@@ -10684,7 +10644,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10695,10 +10655,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10724,16 +10684,16 @@
         <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10782,7 +10742,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10791,7 +10751,7 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10803,10 +10763,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10817,10 +10777,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10935,10 +10895,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11029,7 +10989,7 @@
         <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>122</v>
@@ -11044,7 +11004,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11055,10 +11015,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11084,16 +11044,16 @@
         <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11142,7 +11102,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11151,7 +11111,7 @@
         <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>105</v>
@@ -11163,10 +11123,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11177,10 +11137,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11206,13 +11166,13 @@
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11262,7 +11222,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11271,7 +11231,7 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -11283,10 +11243,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11297,10 +11257,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11326,16 +11286,14 @@
         <v>173</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11384,7 +11342,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11393,7 +11351,7 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11405,10 +11363,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11419,10 +11377,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11448,16 +11406,14 @@
         <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11506,7 +11462,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11515,7 +11471,7 @@
         <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>105</v>
@@ -11527,10 +11483,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11541,10 +11497,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11567,19 +11523,19 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11628,7 +11584,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11637,7 +11593,7 @@
         <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>105</v>
@@ -11649,10 +11605,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11663,10 +11619,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11692,16 +11648,16 @@
         <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11750,7 +11706,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11759,7 +11715,7 @@
         <v>93</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>105</v>
@@ -11771,10 +11727,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11785,14 +11741,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11811,19 +11767,19 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11852,7 +11808,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11870,7 +11826,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11888,27 +11844,27 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>523</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11931,19 +11887,19 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11992,7 +11948,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12013,10 +11969,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12027,10 +11983,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12053,16 +12009,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12091,10 +12047,10 @@
         <v>163</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12112,7 +12068,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12130,27 +12086,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="AM80" t="s" s="2">
+      <c r="AO80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP80" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>541</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12173,19 +12129,19 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12213,10 +12169,10 @@
         <v>163</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12234,7 +12190,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12255,10 +12211,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12269,10 +12225,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12295,16 +12251,16 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12354,7 +12310,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12372,27 +12328,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12415,16 +12371,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12474,7 +12430,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12492,27 +12448,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>568</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12535,19 +12491,19 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12596,7 +12552,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12608,19 +12564,19 @@
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12631,10 +12587,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12749,10 +12705,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12869,14 +12825,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12898,16 +12854,16 @@
         <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12956,7 +12912,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12991,10 +12947,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13017,13 +12973,13 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13074,7 +13030,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13083,7 +13039,7 @@
         <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>105</v>
@@ -13095,10 +13051,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13109,10 +13065,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13135,13 +13091,13 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13192,7 +13148,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13201,7 +13157,7 @@
         <v>93</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>105</v>
@@ -13213,10 +13169,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13227,10 +13183,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13253,19 +13209,19 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13293,10 +13249,10 @@
         <v>177</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13314,7 +13270,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13332,13 +13288,13 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13349,10 +13305,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13375,19 +13331,19 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13412,13 +13368,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>244</v>
+        <v>163</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13436,7 +13392,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13454,13 +13410,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13471,10 +13427,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13497,16 +13453,18 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>611</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>108</v>
+        <v>612</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>109</v>
+        <v>613</v>
       </c>
       <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>614</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13554,7 +13512,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>110</v>
+        <v>610</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13566,7 +13524,7 @@
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -13578,7 +13536,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>111</v>
+        <v>615</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13589,21 +13547,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13615,17 +13573,15 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>115</v>
+        <v>617</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13662,31 +13618,31 @@
         <v>82</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>121</v>
+        <v>616</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -13695,10 +13651,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>196</v>
+        <v>619</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13709,10 +13665,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13735,20 +13691,18 @@
         <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>151</v>
+        <v>621</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>270</v>
+        <v>622</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>271</v>
+        <v>623</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13796,7 +13750,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>274</v>
+        <v>620</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13805,7 +13759,7 @@
         <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>105</v>
@@ -13817,10 +13771,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>275</v>
+        <v>625</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>276</v>
+        <v>626</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13831,10 +13785,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13845,7 +13799,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13854,18 +13808,20 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>107</v>
+        <v>628</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>108</v>
+        <v>629</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>630</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13914,19 +13870,19 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>110</v>
+        <v>627</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -13935,10 +13891,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>111</v>
+        <v>632</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13949,14 +13905,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13966,27 +13922,29 @@
         <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>114</v>
+        <v>568</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>115</v>
+        <v>634</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>116</v>
+        <v>634</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>635</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>636</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -14022,19 +13980,19 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>121</v>
+        <v>633</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14043,10 +14001,10 @@
         <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>122</v>
+        <v>637</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -14055,10 +14013,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>82</v>
+        <v>638</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>196</v>
+        <v>639</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14069,10 +14027,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14080,7 +14038,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>93</v>
@@ -14092,23 +14050,19 @@
         <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>283</v>
+        <v>108</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14156,7 +14110,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>288</v>
+        <v>110</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14165,10 +14119,10 @@
         <v>93</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -14177,10 +14131,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>290</v>
+        <v>111</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14191,21 +14145,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
@@ -14214,19 +14168,19 @@
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>293</v>
+        <v>115</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>294</v>
+        <v>116</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>295</v>
+        <v>117</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14276,19 +14230,19 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>296</v>
+        <v>121</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14297,10 +14251,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>298</v>
+        <v>111</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14311,45 +14265,45 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>619</v>
+        <v>642</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>619</v>
+        <v>642</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>301</v>
+        <v>580</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>302</v>
+        <v>581</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>509</v>
+        <v>117</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>303</v>
+        <v>209</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14398,19 +14352,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>305</v>
+        <v>582</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14419,10 +14373,10 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>307</v>
+        <v>196</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14433,10 +14387,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14444,13 +14398,13 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>82</v>
@@ -14459,19 +14413,19 @@
         <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>107</v>
+        <v>251</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>310</v>
+        <v>644</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>311</v>
+        <v>645</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>509</v>
+        <v>646</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>312</v>
+        <v>647</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14496,13 +14450,13 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14520,16 +14474,16 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>313</v>
+        <v>643</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>105</v>
@@ -14538,16 +14492,16 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>82</v>
+        <v>648</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>82</v>
@@ -14555,10 +14509,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14572,7 +14526,7 @@
         <v>93</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>82</v>
@@ -14581,19 +14535,19 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>318</v>
+        <v>650</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>319</v>
+        <v>651</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>320</v>
+        <v>652</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>321</v>
+        <v>653</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>322</v>
+        <v>431</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14618,13 +14572,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>82</v>
+        <v>654</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>82</v>
+        <v>655</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14642,7 +14596,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>323</v>
+        <v>649</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14651,7 +14605,7 @@
         <v>93</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>206</v>
+        <v>656</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>105</v>
@@ -14660,27 +14614,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>82</v>
+        <v>657</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>324</v>
+        <v>436</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>325</v>
+        <v>437</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>622</v>
+        <v>658</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>622</v>
+        <v>658</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14694,28 +14648,28 @@
         <v>93</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>107</v>
+        <v>251</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>328</v>
+        <v>659</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>329</v>
+        <v>660</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>330</v>
+        <v>661</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>331</v>
+        <v>495</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14740,13 +14694,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14764,7 +14718,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>332</v>
+        <v>658</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14773,7 +14727,7 @@
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>206</v>
+        <v>662</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14785,10 +14739,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>333</v>
+        <v>196</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>334</v>
+        <v>499</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14799,21 +14753,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>623</v>
+        <v>663</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>623</v>
+        <v>663</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -14825,17 +14779,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>624</v>
+        <v>251</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>625</v>
+        <v>513</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="O103" t="s" s="2">
-        <v>627</v>
+        <v>516</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14860,13 +14816,13 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>82</v>
+        <v>664</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14884,13 +14840,13 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>623</v>
+        <v>663</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
@@ -14902,27 +14858,27 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>82</v>
+        <v>518</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>628</v>
+        <v>520</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>629</v>
+        <v>665</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>629</v>
+        <v>665</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14933,7 +14889,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14945,16 +14901,20 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>630</v>
+        <v>666</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>667</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
       </c>
@@ -15002,13 +14962,13 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>629</v>
+        <v>665</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
@@ -15023,1352 +14983,20 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>632</v>
+        <v>575</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="P107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O109" s="2"/>
-      <c r="P109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="P111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="P112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="P113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="P115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP115" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP115">
+  <autoFilter ref="A1:AP104">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16378,7 +15006,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI114">
+  <conditionalFormatting sqref="A2:AI103">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:19:08+00:00</t>
+    <t>2025-03-27T13:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5223,7 +5223,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>238</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>261</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>267</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>280</v>
       </c>
@@ -6427,7 +6427,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>298</v>
       </c>
@@ -6911,7 +6911,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>334</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>371</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>398</v>
       </c>
@@ -9325,7 +9325,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>439</v>
       </c>
@@ -9687,7 +9687,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>445</v>
       </c>
@@ -9931,7 +9931,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>466</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>474</v>
       </c>
@@ -10171,7 +10171,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>483</v>
       </c>
@@ -10293,7 +10293,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>491</v>
       </c>
@@ -12343,7 +12343,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>558</v>
       </c>
@@ -13903,7 +13903,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>633</v>
       </c>
@@ -14385,7 +14385,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>643</v>
       </c>
@@ -14507,7 +14507,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
         <v>649</v>
       </c>
@@ -14629,7 +14629,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
         <v>658</v>
       </c>
@@ -14997,12 +14997,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP104">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$106</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4017" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4093" uniqueCount="678">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,7 +656,40 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t>MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement}
+</t>
+  </si>
+  <si>
+    <t>Motif de la mesure</t>
+  </si>
+  <si>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -1317,7 +1350,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2413,12 +2446,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP104"/>
+  <dimension ref="A1:AP106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.26953125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.3359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2426,7 +2459,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4746,43 +4779,41 @@
         <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>114</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4830,7 +4861,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4854,7 +4885,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4868,9 +4899,11 @@
         <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4879,7 +4912,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4888,21 +4921,19 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>215</v>
-      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4950,7 +4981,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4962,22 +4993,22 @@
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4985,14 +5016,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>221</v>
+        <v>113</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5005,23 +5036,25 @@
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5082,19 +5115,19 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5105,14 +5138,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5131,18 +5164,18 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5190,7 +5223,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5205,65 +5238,63 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5288,11 +5319,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5310,13 +5343,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -5325,19 +5358,19 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5345,46 +5378,44 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5408,29 +5439,31 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5445,19 +5478,19 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5465,14 +5498,12 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5487,25 +5518,25 @@
         <v>94</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5530,13 +5561,11 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5554,13 +5583,13 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -5569,19 +5598,19 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5589,10 +5618,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5600,13 +5629,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -5615,16 +5644,20 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>107</v>
+        <v>261</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>108</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5648,43 +5681,41 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5696,35 +5727,37 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>111</v>
+        <v>269</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
@@ -5733,18 +5766,20 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>114</v>
+        <v>261</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>115</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>116</v>
+        <v>263</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5768,31 +5803,31 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>121</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5804,7 +5839,7 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5816,21 +5851,21 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>111</v>
+        <v>269</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5838,35 +5873,31 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>269</v>
+        <v>108</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5914,19 +5945,19 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>273</v>
+        <v>110</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5935,10 +5966,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>275</v>
+        <v>111</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5949,21 +5980,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5975,15 +6006,17 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -6020,31 +6053,31 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6065,46 +6098,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>115</v>
+        <v>279</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>116</v>
+        <v>280</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6140,19 +6175,19 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>121</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6164,7 +6199,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6173,10 +6208,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6185,12 +6220,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6198,41 +6233,37 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>82</v>
@@ -6274,7 +6305,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6286,7 +6317,7 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6295,10 +6326,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>289</v>
+        <v>111</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6309,21 +6340,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6332,19 +6363,19 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>292</v>
+        <v>115</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
+        <v>116</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>294</v>
+        <v>117</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6382,31 +6413,31 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>121</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6415,10 +6446,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>297</v>
+        <v>111</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6429,10 +6460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6455,24 +6486,26 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6514,7 +6547,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6535,10 +6568,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6549,10 +6582,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6578,15 +6611,15 @@
         <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6634,7 +6667,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6655,10 +6688,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6667,12 +6700,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6680,13 +6713,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6695,26 +6728,24 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>317</v>
+        <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6756,7 +6787,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6777,10 +6808,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6791,10 +6822,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6820,16 +6851,14 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6878,7 +6907,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6899,10 +6928,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6911,26 +6940,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6939,19 +6968,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>251</v>
+        <v>327</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6976,13 +7005,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -7000,10 +7029,10 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>93</v>
@@ -7015,30 +7044,30 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7058,19 +7087,23 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>108</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7118,7 +7151,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>110</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7130,7 +7163,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -7139,10 +7172,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>111</v>
+        <v>343</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7151,46 +7184,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>113</v>
+        <v>345</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>114</v>
+        <v>261</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>115</v>
+        <v>346</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>116</v>
+        <v>347</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7214,69 +7249,69 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>121</v>
+        <v>344</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>111</v>
+        <v>355</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7284,10 +7319,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7296,23 +7331,19 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>269</v>
+        <v>108</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7348,29 +7379,31 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>273</v>
+        <v>110</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7379,10 +7412,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>275</v>
+        <v>111</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7393,23 +7426,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7418,23 +7449,21 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>269</v>
+        <v>115</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>270</v>
+        <v>116</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7470,19 +7499,19 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>273</v>
+        <v>121</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7494,7 +7523,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7503,10 +7532,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>275</v>
+        <v>111</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7517,10 +7546,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7528,10 +7557,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7540,19 +7569,23 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7588,31 +7621,29 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7621,10 +7652,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7635,21 +7666,23 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="D44" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7658,21 +7691,23 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>115</v>
+        <v>279</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>116</v>
+        <v>280</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7708,19 +7743,19 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>121</v>
+        <v>283</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7732,7 +7767,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7741,10 +7776,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7755,10 +7790,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7766,7 +7801,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>93</v>
@@ -7778,29 +7813,25 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>82</v>
@@ -7842,7 +7873,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7854,7 +7885,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7863,10 +7894,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>289</v>
+        <v>111</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7877,21 +7908,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7900,19 +7931,19 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>292</v>
+        <v>115</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>293</v>
+        <v>116</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>294</v>
+        <v>117</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7950,31 +7981,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>295</v>
+        <v>121</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7983,10 +8014,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>297</v>
+        <v>111</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7997,10 +8028,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8023,24 +8054,26 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -8082,7 +8115,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8103,10 +8136,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8117,10 +8150,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8146,15 +8179,15 @@
         <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8202,7 +8235,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8223,10 +8256,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8237,10 +8270,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8248,7 +8281,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -8263,26 +8296,24 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>317</v>
+        <v>173</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8324,7 +8355,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8345,10 +8376,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8359,10 +8390,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8388,16 +8419,14 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8446,7 +8475,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8467,10 +8496,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8479,12 +8508,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8492,13 +8521,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
@@ -8507,19 +8536,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>373</v>
+        <v>328</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8568,7 +8597,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>371</v>
+        <v>332</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8583,19 +8612,19 @@
         <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>379</v>
+        <v>334</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8603,10 +8632,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8617,7 +8646,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8629,18 +8658,20 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>382</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>383</v>
+        <v>337</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8688,13 +8719,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>381</v>
+        <v>341</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8709,38 +8740,38 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>386</v>
+        <v>343</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8749,19 +8780,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8810,7 +8841,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8825,44 +8856,44 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -8871,20 +8902,18 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8932,34 +8961,34 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>406</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>408</v>
+        <v>354</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8967,14 +8996,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8993,18 +9022,20 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>129</v>
+        <v>399</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9052,7 +9083,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9067,44 +9098,44 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9113,17 +9144,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9172,34 +9205,34 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="AN56" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9207,10 +9240,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9224,7 +9257,7 @@
         <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
@@ -9233,20 +9266,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>428</v>
+        <v>129</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9282,17 +9313,19 @@
         <v>82</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AC57" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9301,7 +9334,7 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -9310,43 +9343,41 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9355,19 +9386,17 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9416,45 +9445,45 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AN58" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP58" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9468,25 +9497,29 @@
         <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>108</v>
+        <v>439</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9522,19 +9555,17 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>110</v>
+        <v>437</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9543,70 +9574,74 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>111</v>
+        <v>447</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="D60" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>114</v>
+        <v>438</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>115</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>116</v>
+        <v>439</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9642,57 +9677,57 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>121</v>
+        <v>437</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>111</v>
+        <v>447</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9700,35 +9735,31 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>447</v>
+        <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>448</v>
+        <v>108</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9776,7 +9807,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>452</v>
+        <v>110</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9788,7 +9819,7 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9797,10 +9828,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>454</v>
+        <v>111</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9811,50 +9842,48 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>457</v>
+        <v>115</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q62" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9874,43 +9903,43 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>461</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>462</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>463</v>
+        <v>121</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9919,10 +9948,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>465</v>
+        <v>111</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9933,10 +9962,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9959,17 +9988,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>107</v>
+        <v>457</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10018,7 +10049,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10039,10 +10070,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10051,12 +10082,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10064,39 +10095,41 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q64" s="2"/>
+      <c r="Q64" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="R64" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>82</v>
@@ -10114,13 +10147,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -10138,7 +10171,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10147,7 +10180,7 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -10159,10 +10192,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10173,10 +10206,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10199,26 +10232,24 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>488</v>
+        <v>82</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>82</v>
@@ -10260,7 +10291,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10281,10 +10312,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10295,10 +10326,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10306,7 +10337,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>93</v>
@@ -10318,29 +10349,27 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>251</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>82</v>
@@ -10358,13 +10387,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10382,16 +10411,16 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI66" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10403,10 +10432,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>196</v>
+        <v>482</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10415,12 +10444,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10428,37 +10457,41 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>108</v>
+        <v>495</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>82</v>
@@ -10500,7 +10533,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>110</v>
+        <v>499</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10512,7 +10545,7 @@
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10521,10 +10554,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>111</v>
+        <v>500</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10533,7 +10566,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>501</v>
       </c>
@@ -10542,17 +10575,17 @@
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
@@ -10561,18 +10594,20 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>114</v>
+        <v>261</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>115</v>
+        <v>502</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>116</v>
+        <v>503</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10596,43 +10631,43 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>121</v>
+        <v>501</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>508</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10641,10 +10676,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>111</v>
+        <v>509</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10655,10 +10690,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10669,7 +10704,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10678,23 +10713,19 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>269</v>
+        <v>108</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10742,19 +10773,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>273</v>
+        <v>110</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10763,10 +10794,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>275</v>
+        <v>111</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10777,21 +10808,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10803,15 +10834,17 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10848,31 +10881,31 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10895,14 +10928,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10918,21 +10951,23 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>115</v>
+        <v>279</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>116</v>
+        <v>280</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10968,19 +11003,19 @@
         <v>82</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>121</v>
+        <v>283</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10992,7 +11027,7 @@
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11001,10 +11036,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11015,10 +11050,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11026,7 +11061,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>93</v>
@@ -11038,23 +11073,19 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11102,7 +11133,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11114,7 +11145,7 @@
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11123,10 +11154,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>289</v>
+        <v>111</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11137,21 +11168,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11160,19 +11191,19 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>292</v>
+        <v>115</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>293</v>
+        <v>116</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>294</v>
+        <v>117</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11210,31 +11241,31 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>295</v>
+        <v>121</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11243,10 +11274,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>297</v>
+        <v>111</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11257,10 +11288,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11283,17 +11314,19 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="O74" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11342,7 +11375,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11363,10 +11396,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11377,10 +11410,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11406,15 +11439,15 @@
         <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11462,7 +11495,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11483,10 +11516,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11497,10 +11530,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11508,7 +11541,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>93</v>
@@ -11523,19 +11556,17 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>317</v>
+        <v>173</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11584,7 +11615,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11605,10 +11636,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11619,10 +11650,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11648,16 +11679,14 @@
         <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11706,7 +11735,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11727,10 +11756,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11741,21 +11770,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>512</v>
+        <v>82</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11764,22 +11793,22 @@
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>251</v>
+        <v>327</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>513</v>
+        <v>328</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>514</v>
+        <v>329</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>515</v>
+        <v>330</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>516</v>
+        <v>331</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11804,11 +11833,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11826,13 +11857,13 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>511</v>
+        <v>332</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
@@ -11844,27 +11875,27 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>519</v>
+        <v>333</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>520</v>
+        <v>334</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11875,7 +11906,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11884,22 +11915,22 @@
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>523</v>
+        <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>524</v>
+        <v>337</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>525</v>
+        <v>338</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>526</v>
+        <v>339</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>527</v>
+        <v>340</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11948,13 +11979,13 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>522</v>
+        <v>341</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
@@ -11969,10 +12000,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>528</v>
+        <v>342</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>529</v>
+        <v>343</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11983,21 +12014,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -12009,18 +12040,20 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -12044,13 +12077,11 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12068,13 +12099,13 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
@@ -12086,27 +12117,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>539</v>
+        <v>531</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12117,7 +12148,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12129,19 +12160,19 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>251</v>
+        <v>533</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12166,13 +12197,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12190,13 +12221,13 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
@@ -12211,10 +12242,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12225,10 +12256,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12251,16 +12282,16 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>550</v>
+        <v>261</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12286,13 +12317,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12310,7 +12341,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12328,27 +12359,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12362,7 +12393,7 @@
         <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>82</v>
@@ -12371,18 +12402,20 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>559</v>
+        <v>261</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12406,13 +12439,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>82</v>
+        <v>555</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>82</v>
+        <v>556</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12430,7 +12463,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12448,27 +12481,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12479,7 +12512,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12491,20 +12524,18 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12552,45 +12583,45 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP84" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AG84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12604,7 +12635,7 @@
         <v>93</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>82</v>
@@ -12613,15 +12644,17 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>107</v>
+        <v>569</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>108</v>
+        <v>570</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12670,7 +12703,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>110</v>
+        <v>568</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12682,25 +12715,25 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>574</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>111</v>
+        <v>575</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>82</v>
+        <v>576</v>
       </c>
     </row>
     <row r="86" hidden="true">
@@ -12712,7 +12745,7 @@
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12731,18 +12764,20 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>114</v>
+        <v>578</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>115</v>
+        <v>579</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>116</v>
+        <v>580</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12790,7 +12825,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>121</v>
+        <v>577</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12802,7 +12837,7 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>122</v>
+        <v>583</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12811,10 +12846,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>82</v>
+        <v>584</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>111</v>
+        <v>585</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12825,46 +12860,42 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>580</v>
+        <v>108</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12912,19 +12943,19 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>582</v>
+        <v>110</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12936,7 +12967,7 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12947,21 +12978,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12973,15 +13004,17 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>584</v>
+        <v>114</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>585</v>
+        <v>115</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13030,19 +13063,19 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>583</v>
+        <v>121</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -13051,10 +13084,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>588</v>
+        <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>589</v>
+        <v>111</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13065,42 +13098,46 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>584</v>
+        <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+      <c r="N89" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13148,19 +13185,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13169,10 +13206,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>588</v>
+        <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>593</v>
+        <v>196</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13183,10 +13220,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13209,7 +13246,7 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>251</v>
+        <v>594</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>595</v>
@@ -13217,12 +13254,8 @@
       <c r="M90" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N90" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>598</v>
-      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13246,13 +13279,13 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>600</v>
+        <v>82</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13270,7 +13303,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13279,7 +13312,7 @@
         <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>105</v>
@@ -13288,13 +13321,13 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>601</v>
+        <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>520</v>
+        <v>599</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13305,10 +13338,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13319,7 +13352,7 @@
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13331,20 +13364,16 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>251</v>
+        <v>594</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>607</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13368,13 +13397,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>608</v>
+        <v>82</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13392,16 +13421,16 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>105</v>
@@ -13410,13 +13439,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>601</v>
+        <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>520</v>
+        <v>603</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13427,10 +13456,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13453,17 +13482,19 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>611</v>
+        <v>261</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>606</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>607</v>
+      </c>
       <c r="O92" t="s" s="2">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13488,13 +13519,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>82</v>
+        <v>609</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13512,7 +13543,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13530,13 +13561,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>82</v>
+        <v>612</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>615</v>
+        <v>530</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13547,10 +13578,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13561,7 +13592,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13573,16 +13604,20 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>107</v>
+        <v>261</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="O93" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="M93" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13606,13 +13641,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>82</v>
+        <v>619</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13630,13 +13665,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13648,13 +13683,13 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>588</v>
+        <v>612</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>619</v>
+        <v>530</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13679,7 +13714,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13688,7 +13723,7 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>621</v>
@@ -13699,10 +13734,10 @@
       <c r="M94" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="N94" s="2"/>
+      <c r="O94" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13756,7 +13791,7 @@
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
@@ -13771,10 +13806,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13785,10 +13820,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13799,7 +13834,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13808,20 +13843,18 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L95" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>631</v>
-      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13870,13 +13903,13 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
@@ -13891,10 +13924,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>625</v>
+        <v>598</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13903,12 +13936,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13922,7 +13955,7 @@
         <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
@@ -13931,20 +13964,18 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>568</v>
+        <v>631</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>636</v>
-      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -13992,7 +14023,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14004,7 +14035,7 @@
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>637</v>
+        <v>105</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -14013,10 +14044,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14027,10 +14058,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14041,7 +14072,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -14050,18 +14081,20 @@
         <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>107</v>
+        <v>638</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>108</v>
+        <v>639</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>640</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14110,19 +14143,19 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>110</v>
+        <v>637</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -14131,10 +14164,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>82</v>
+        <v>635</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>111</v>
+        <v>642</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14143,16 +14176,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14162,27 +14195,29 @@
         <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>114</v>
+        <v>578</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>115</v>
+        <v>644</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>116</v>
+        <v>644</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>645</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14230,7 +14265,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>121</v>
+        <v>643</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14242,7 +14277,7 @@
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>122</v>
+        <v>647</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14251,10 +14286,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>82</v>
+        <v>648</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>111</v>
+        <v>649</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14265,46 +14300,42 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>580</v>
+        <v>108</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14352,19 +14383,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>582</v>
+        <v>110</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14376,7 +14407,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14385,48 +14416,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>251</v>
+        <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>644</v>
+        <v>115</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>645</v>
+        <v>116</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>647</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14450,13 +14479,13 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14474,80 +14503,80 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>643</v>
+        <v>121</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>648</v>
+        <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>345</v>
+        <v>111</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I101" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>650</v>
+        <v>114</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>651</v>
+        <v>590</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>652</v>
+        <v>591</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>653</v>
+        <v>117</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>431</v>
+        <v>219</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14572,13 +14601,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>654</v>
+        <v>82</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>655</v>
+        <v>82</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14596,45 +14625,45 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>649</v>
+        <v>592</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>656</v>
+        <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>657</v>
+        <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>437</v>
+        <v>196</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14642,7 +14671,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>93</v>
@@ -14654,22 +14683,22 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>495</v>
+        <v>657</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14697,10 +14726,10 @@
         <v>155</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>496</v>
+        <v>350</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>497</v>
+        <v>351</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14718,16 +14747,16 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>662</v>
+        <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14736,62 +14765,62 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>82</v>
+        <v>658</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>196</v>
+        <v>354</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>499</v>
+        <v>355</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>512</v>
+        <v>82</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>251</v>
+        <v>660</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>513</v>
+        <v>661</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>514</v>
+        <v>662</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>515</v>
+        <v>663</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>516</v>
+        <v>441</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14822,7 +14851,7 @@
         <v>664</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>517</v>
+        <v>665</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14840,16 +14869,16 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>82</v>
+        <v>666</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14858,27 +14887,27 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>518</v>
+        <v>667</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>519</v>
+        <v>446</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>520</v>
+        <v>447</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>521</v>
+        <v>448</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14889,10 +14918,10 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>82</v>
@@ -14901,19 +14930,19 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>83</v>
+        <v>261</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>571</v>
+        <v>671</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>572</v>
+        <v>505</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14938,13 +14967,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14962,16 +14991,16 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>82</v>
+        <v>672</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -14983,20 +15012,264 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>574</v>
+        <v>196</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>575</v>
+        <v>509</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="P105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP106" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP104">
+  <autoFilter ref="A1:AP106">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15006,7 +15279,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI103">
+  <conditionalFormatting sqref="A2:AI105">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$105</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4093" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4055" uniqueCount="673">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -674,22 +674,6 @@
   <si>
     <t>Motif de la mesure
 Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
-  </si>
-  <si>
-    <t>Observation.extension:MesOriginOfData</t>
-  </si>
-  <si>
-    <t>MesOriginOfData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
-</t>
-  </si>
-  <si>
-    <t>Origine de la donnée</t>
-  </si>
-  <si>
-    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -2446,7 +2430,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP106"/>
+  <dimension ref="A1:AP105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.26953125" customWidth="true" bestFit="true"/>
@@ -4899,41 +4883,43 @@
         <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4981,7 +4967,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5005,7 +4991,7 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -5023,7 +5009,7 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5036,25 +5022,23 @@
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J22" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5103,7 +5087,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5115,22 +5099,22 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>82</v>
+        <v>222</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5138,14 +5122,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5164,17 +5148,17 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5223,7 +5207,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5238,19 +5222,19 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -5258,14 +5242,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5284,18 +5268,18 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5343,7 +5327,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5358,16 +5342,16 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5376,46 +5360,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5439,13 +5425,11 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5463,13 +5447,13 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5478,30 +5462,30 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5512,31 +5496,31 @@
         <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5561,35 +5545,35 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -5598,32 +5582,34 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5632,7 +5618,7 @@
         <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>94</v>
@@ -5644,19 +5630,19 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5684,26 +5670,28 @@
         <v>177</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AC27" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5727,37 +5715,35 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AO27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>272</v>
-      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
@@ -5766,20 +5752,16 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5803,13 +5785,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5827,19 +5809,19 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5851,10 +5833,10 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5862,21 +5844,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5888,15 +5870,17 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5933,31 +5917,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5978,46 +5962,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>115</v>
+        <v>274</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>116</v>
+        <v>275</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6053,19 +6039,19 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>121</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6077,7 +6063,7 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6086,10 +6072,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6098,12 +6084,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6111,35 +6097,31 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6187,19 +6169,19 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6208,10 +6190,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6222,21 +6204,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6248,15 +6230,17 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6293,31 +6277,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6338,52 +6322,54 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>82</v>
@@ -6413,31 +6399,31 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>121</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6446,10 +6432,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>111</v>
+        <v>294</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6458,12 +6444,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6471,13 +6457,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6486,26 +6472,24 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6547,7 +6531,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6568,10 +6552,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6580,12 +6564,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6593,13 +6577,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6608,24 +6592,24 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6667,7 +6651,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6688,10 +6672,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6700,12 +6684,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6713,13 +6697,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6728,24 +6712,24 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6787,7 +6771,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6808,10 +6792,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6822,10 +6806,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6848,17 +6832,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>322</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6907,7 +6893,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6928,10 +6914,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6942,10 +6928,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6968,19 +6954,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7029,7 +7015,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7050,10 +7036,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7062,26 +7048,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -7090,19 +7076,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7127,13 +7113,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7151,10 +7137,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7166,66 +7152,62 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>346</v>
+        <v>108</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7249,13 +7231,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7273,10 +7255,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>110</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>93</v>
@@ -7285,44 +7267,44 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>355</v>
+        <v>111</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7334,15 +7316,17 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7379,31 +7363,31 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7426,18 +7410,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>81</v>
@@ -7449,21 +7433,23 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>115</v>
+        <v>274</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>116</v>
+        <v>275</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7499,11 +7485,9 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7511,7 +7495,7 @@
         <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>121</v>
+        <v>278</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7523,7 +7507,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7532,10 +7516,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7546,12 +7530,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7560,7 +7546,7 @@
         <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7575,16 +7561,16 @@
         <v>151</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7621,17 +7607,19 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7652,10 +7640,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7666,20 +7654,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="C44" t="s" s="2">
-        <v>363</v>
-      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
@@ -7691,23 +7677,19 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7755,19 +7737,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7776,10 +7758,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7790,21 +7772,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7816,15 +7798,17 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7861,31 +7845,31 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7908,21 +7892,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7931,27 +7915,29 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>82</v>
@@ -7981,31 +7967,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>121</v>
+        <v>292</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8014,10 +8000,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>111</v>
+        <v>294</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8028,10 +8014,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8039,7 +8025,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -8054,26 +8040,24 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -8115,7 +8099,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8136,10 +8120,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8150,10 +8134,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8161,7 +8145,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8176,24 +8160,24 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8235,7 +8219,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8256,10 +8240,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8270,10 +8254,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8281,7 +8265,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -8296,24 +8280,24 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8355,7 +8339,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8376,10 +8360,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8390,10 +8374,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8416,17 +8400,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>322</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8475,7 +8461,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8496,10 +8482,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8510,10 +8496,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8536,19 +8522,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8597,7 +8583,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8618,10 +8604,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8630,12 +8616,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8643,13 +8629,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -8658,19 +8644,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>377</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8719,7 +8705,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>341</v>
+        <v>376</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8734,30 +8720,30 @@
         <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8765,13 +8751,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8780,20 +8766,18 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8841,13 +8825,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8856,19 +8840,19 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>388</v>
+        <v>349</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8876,21 +8860,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8902,18 +8886,20 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8961,13 +8947,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8976,44 +8962,44 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9022,19 +9008,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9083,7 +9069,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9092,50 +9078,50 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9144,20 +9130,18 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>410</v>
+        <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9205,7 +9189,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9214,25 +9198,25 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>416</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9240,10 +9224,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9254,7 +9238,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9266,18 +9250,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>129</v>
+        <v>424</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9325,13 +9309,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9340,19 +9324,19 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9360,10 +9344,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9374,10 +9358,10 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9386,17 +9370,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9433,65 +9419,65 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>93</v>
@@ -9506,19 +9492,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9555,17 +9541,19 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AC59" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9574,7 +9562,7 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9583,65 +9571,59 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="B60" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AO59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>450</v>
-      </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>438</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>439</v>
+        <v>108</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9689,7 +9671,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>110</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9698,47 +9680,47 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>447</v>
+        <v>111</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9750,15 +9732,17 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9795,31 +9779,31 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9840,46 +9824,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>114</v>
+        <v>452</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>115</v>
+        <v>453</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>116</v>
+        <v>454</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9915,31 +9901,31 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>121</v>
+        <v>457</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9948,10 +9934,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>111</v>
+        <v>459</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9960,12 +9946,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9973,39 +9959,39 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>457</v>
+        <v>173</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="R63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10025,13 +10011,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10049,7 +10035,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10070,10 +10056,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10082,12 +10068,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10095,39 +10081,37 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q64" t="s" s="2">
-        <v>470</v>
-      </c>
+      <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10147,13 +10131,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -10171,7 +10155,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10192,10 +10176,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10206,10 +10190,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10232,24 +10216,24 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>82</v>
@@ -10291,7 +10275,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10300,7 +10284,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -10312,10 +10296,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10326,10 +10310,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10352,24 +10336,26 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>82</v>
@@ -10411,7 +10397,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10420,7 +10406,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10432,10 +10418,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10446,10 +10432,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10457,7 +10443,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
@@ -10469,29 +10455,29 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>82</v>
@@ -10509,13 +10495,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10533,7 +10519,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10542,7 +10528,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10554,10 +10540,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>482</v>
+        <v>196</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10566,12 +10552,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10585,7 +10571,7 @@
         <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
@@ -10594,20 +10580,16 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>502</v>
+        <v>108</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10631,13 +10613,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>507</v>
+        <v>82</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10655,7 +10637,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>501</v>
+        <v>110</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10664,10 +10646,10 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10676,10 +10658,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>509</v>
+        <v>111</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10690,21 +10672,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10716,15 +10698,17 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10761,31 +10745,31 @@
         <v>82</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10808,14 +10792,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10831,21 +10815,23 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>115</v>
+        <v>274</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>116</v>
+        <v>275</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10881,19 +10867,19 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>121</v>
+        <v>278</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10905,7 +10891,7 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10914,10 +10900,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10928,10 +10914,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10942,7 +10928,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10951,23 +10937,19 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11015,19 +10997,19 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11036,10 +11018,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11050,21 +11032,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11076,15 +11058,17 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11121,31 +11105,31 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11168,21 +11152,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11191,21 +11175,23 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11241,31 +11227,31 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>121</v>
+        <v>292</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11274,10 +11260,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>111</v>
+        <v>294</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11288,10 +11274,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11299,7 +11285,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>93</v>
@@ -11314,20 +11300,18 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11375,7 +11359,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11396,10 +11380,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11410,10 +11394,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11421,7 +11405,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>93</v>
@@ -11436,18 +11420,18 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11495,7 +11479,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11516,10 +11500,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11530,10 +11514,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11541,7 +11525,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>93</v>
@@ -11556,17 +11540,17 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11615,7 +11599,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11636,10 +11620,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11650,10 +11634,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11676,17 +11660,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>107</v>
+        <v>322</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O77" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11735,7 +11721,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11756,10 +11742,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11770,10 +11756,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11796,19 +11782,19 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11857,7 +11843,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11878,10 +11864,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11892,21 +11878,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11915,22 +11901,22 @@
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>337</v>
+        <v>518</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>338</v>
+        <v>519</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>339</v>
+        <v>520</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>340</v>
+        <v>521</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11955,13 +11941,11 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11979,13 +11963,13 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>341</v>
+        <v>516</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
@@ -11997,31 +11981,31 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>342</v>
+        <v>524</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>343</v>
+        <v>525</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12040,19 +12024,19 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>261</v>
+        <v>528</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12077,29 +12061,31 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12117,27 +12103,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12148,7 +12134,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12160,20 +12146,18 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>533</v>
+        <v>256</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12197,13 +12181,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12221,13 +12205,13 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
@@ -12239,27 +12223,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12282,18 +12266,20 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12320,28 +12306,28 @@
         <v>163</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="Z82" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12359,27 +12345,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12402,20 +12388,18 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>261</v>
+        <v>555</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12439,13 +12423,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12463,7 +12447,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12481,27 +12465,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>559</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12515,7 +12499,7 @@
         <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12524,16 +12508,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12583,7 +12567,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12601,27 +12585,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12632,10 +12616,10 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>82</v>
@@ -12644,18 +12628,20 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12703,45 +12689,45 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>105</v>
+        <v>578</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>573</v>
+        <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12752,7 +12738,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12764,20 +12750,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>578</v>
+        <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>579</v>
+        <v>108</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12825,19 +12807,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>577</v>
+        <v>110</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>583</v>
+        <v>82</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12846,10 +12828,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>584</v>
+        <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>585</v>
+        <v>111</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12860,21 +12842,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12886,15 +12868,17 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12943,19 +12927,19 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12978,14 +12962,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>113</v>
+        <v>584</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12998,24 +12982,26 @@
         <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>115</v>
+        <v>585</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>116</v>
+        <v>586</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -13063,7 +13049,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>121</v>
+        <v>587</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13087,7 +13073,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13105,26 +13091,26 @@
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>114</v>
+        <v>589</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>590</v>
@@ -13132,12 +13118,8 @@
       <c r="M89" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="N89" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>219</v>
-      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13185,19 +13167,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI89" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AG89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AJ89" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13206,10 +13188,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>82</v>
+        <v>593</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>196</v>
+        <v>594</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13220,10 +13202,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13246,13 +13228,13 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13303,7 +13285,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13312,7 +13294,7 @@
         <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>105</v>
@@ -13324,10 +13306,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13338,10 +13320,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13364,16 +13346,20 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>594</v>
+        <v>256</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>603</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13397,13 +13383,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>82</v>
+        <v>604</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13421,7 +13407,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13430,7 +13416,7 @@
         <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>597</v>
+        <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>105</v>
@@ -13439,13 +13425,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>603</v>
+        <v>525</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13456,10 +13442,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13470,7 +13456,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13482,19 +13468,19 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13519,13 +13505,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13543,13 +13529,13 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
@@ -13561,13 +13547,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13578,10 +13564,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13592,7 +13578,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13604,19 +13590,17 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>261</v>
+        <v>616</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13641,13 +13625,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>618</v>
+        <v>82</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>619</v>
+        <v>82</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13665,13 +13649,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13683,13 +13667,13 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>612</v>
+        <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>530</v>
+        <v>620</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13700,10 +13684,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13726,7 +13710,7 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>621</v>
+        <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>622</v>
@@ -13735,9 +13719,7 @@
         <v>623</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>624</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13785,7 +13767,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13806,10 +13788,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>82</v>
+        <v>593</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13820,10 +13802,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13834,7 +13816,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13843,10 +13825,10 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>107</v>
+        <v>626</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>627</v>
@@ -13854,7 +13836,9 @@
       <c r="M95" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="N95" s="2"/>
+      <c r="N95" t="s" s="2">
+        <v>629</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13903,13 +13887,13 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
@@ -13924,10 +13908,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>598</v>
+        <v>630</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13938,10 +13922,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13964,16 +13948,16 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14023,7 +14007,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14044,10 +14028,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14056,12 +14040,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14075,7 +14059,7 @@
         <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>82</v>
@@ -14084,18 +14068,20 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>638</v>
+        <v>573</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>639</v>
       </c>
       <c r="M97" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14143,7 +14129,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14155,7 +14141,7 @@
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>105</v>
+        <v>642</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -14164,10 +14150,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14176,12 +14162,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14192,32 +14178,28 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>578</v>
+        <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>644</v>
+        <v>108</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>646</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14265,19 +14247,19 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>643</v>
+        <v>110</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>647</v>
+        <v>82</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14286,10 +14268,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>648</v>
+        <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>649</v>
+        <v>111</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14300,21 +14282,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14326,15 +14308,17 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14383,19 +14367,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14418,14 +14402,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>113</v>
+        <v>584</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14438,24 +14422,26 @@
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>115</v>
+        <v>585</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>116</v>
+        <v>586</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14503,7 +14489,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>121</v>
+        <v>587</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14527,7 +14513,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14536,47 +14522,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>114</v>
+        <v>256</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>590</v>
+        <v>649</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>591</v>
+        <v>650</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>117</v>
+        <v>651</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>219</v>
+        <v>652</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14601,13 +14587,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14625,34 +14611,34 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>592</v>
+        <v>648</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>82</v>
+        <v>653</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>196</v>
+        <v>350</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>82</v>
@@ -14660,10 +14646,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14671,7 +14657,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>93</v>
@@ -14686,19 +14672,19 @@
         <v>94</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>261</v>
+        <v>655</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>657</v>
+        <v>436</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14726,10 +14712,10 @@
         <v>155</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>350</v>
+        <v>659</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>351</v>
+        <v>660</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14747,16 +14733,16 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>82</v>
+        <v>661</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14765,27 +14751,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>354</v>
+        <v>441</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>355</v>
+        <v>442</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14805,22 +14791,22 @@
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>660</v>
+        <v>256</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>441</v>
+        <v>500</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14848,10 +14834,10 @@
         <v>155</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>664</v>
+        <v>501</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>665</v>
+        <v>502</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14869,7 +14855,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14878,7 +14864,7 @@
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14887,22 +14873,22 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>667</v>
+        <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>446</v>
+        <v>196</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>447</v>
+        <v>504</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
         <v>668</v>
       </c>
@@ -14911,17 +14897,17 @@
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>82</v>
@@ -14930,19 +14916,19 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>669</v>
+        <v>518</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>670</v>
+        <v>519</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>671</v>
+        <v>520</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14970,10 +14956,10 @@
         <v>155</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>506</v>
+        <v>669</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14997,10 +14983,10 @@
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>672</v>
+        <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -15009,31 +14995,31 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>196</v>
+        <v>524</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -15052,19 +15038,19 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>261</v>
+        <v>83</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>523</v>
+        <v>671</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>524</v>
+        <v>672</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>525</v>
+        <v>576</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>526</v>
+        <v>577</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15089,13 +15075,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>674</v>
+        <v>82</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15113,7 +15099,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15131,145 +15117,23 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>529</v>
+        <v>579</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>530</v>
+        <v>580</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP106" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP106">
+  <autoFilter ref="A1:AP105">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15279,7 +15143,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI105">
+  <conditionalFormatting sqref="A2:AI104">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
